--- a/frontend/static/sample/sample_dcf_report.xlsx
+++ b/frontend/static/sample/sample_dcf_report.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-27 · Confidential — prepared for internal review</t>
+          <t>Generated 2026-09-03 · Confidential — prepared for internal review</t>
         </is>
       </c>
     </row>
